--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8685,6 +8685,69 @@
       <c r="E393" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>331.01</v>
+      </c>
+      <c r="C394" t="n">
+        <v>210.95</v>
+      </c>
+      <c r="D394" t="n">
+        <v>203.9</v>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>330.17</v>
+      </c>
+      <c r="C395" t="n">
+        <v>210.35</v>
+      </c>
+      <c r="D395" t="n">
+        <v>202.98</v>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>330.23</v>
+      </c>
+      <c r="C396" t="n">
+        <v>210.13</v>
+      </c>
+      <c r="D396" t="n">
+        <v>203.8</v>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B624"/>
+  <dimension ref="A1:B628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14942,6 +15005,46 @@
       </c>
       <c r="B624" t="n">
         <v>-0.22</v>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B625" t="n">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B626" t="n">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B627" t="n">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B628" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>
@@ -15104,28 +15207,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.392618902313765</v>
+        <v>1.413337848603623</v>
       </c>
       <c r="J2" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K2" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2165373402473914</v>
+        <v>0.2235970692499609</v>
       </c>
       <c r="M2" t="n">
-        <v>12.84065283367073</v>
+        <v>12.80482335774865</v>
       </c>
       <c r="N2" t="n">
-        <v>309.4051133984384</v>
+        <v>308.2734871363189</v>
       </c>
       <c r="O2" t="n">
-        <v>17.58991510492414</v>
+        <v>17.55771873383097</v>
       </c>
       <c r="P2" t="n">
-        <v>280.5951632666042</v>
+        <v>280.3371181530229</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15176,28 +15279,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5616085538911243</v>
+        <v>-0.5861111559299316</v>
       </c>
       <c r="J3" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K3" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01644707438238524</v>
+        <v>0.01812643211654297</v>
       </c>
       <c r="M3" t="n">
-        <v>19.41463385875939</v>
+        <v>19.33382838831832</v>
       </c>
       <c r="N3" t="n">
-        <v>833.5505073408721</v>
+        <v>828.9074208989597</v>
       </c>
       <c r="O3" t="n">
-        <v>28.87127477859043</v>
+        <v>28.7907523503461</v>
       </c>
       <c r="P3" t="n">
-        <v>240.5547530757437</v>
+        <v>240.8596079056245</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15248,28 +15351,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.486298945585882</v>
+        <v>-1.501196137332423</v>
       </c>
       <c r="J4" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K4" t="n">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1603556438616762</v>
+        <v>0.1650222552737496</v>
       </c>
       <c r="M4" t="n">
-        <v>11.99248990021497</v>
+        <v>11.95113750873847</v>
       </c>
       <c r="N4" t="n">
-        <v>510.0360497880492</v>
+        <v>506.7927526989143</v>
       </c>
       <c r="O4" t="n">
-        <v>22.58397772289127</v>
+        <v>22.51205794011099</v>
       </c>
       <c r="P4" t="n">
-        <v>252.3271361023278</v>
+        <v>252.5126776786404</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15307,7 +15410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E393"/>
+  <dimension ref="A1:E396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25917,6 +26020,87 @@
         </is>
       </c>
     </row>
+    <row r="394">
+      <c r="A394" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>-36.891747109907776,174.98708052704583</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>-36.89222659379522,174.98858511324158</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>-36.892917458051805,174.9887137693927</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:06:01+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>-36.89174553197349,174.98708974375796</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>-36.89222546661548,174.9885916966223</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>-36.89291792295663,174.98872407455357</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>-36.89174564468311,174.9870890854214</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>-36.89222505331614,174.98859411052854</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>-36.89291750858498,174.98871488951886</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8748,6 +8748,27 @@
       <c r="E396" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="C397" t="n">
+        <v>213.53</v>
+      </c>
+      <c r="D397" t="n">
+        <v>202.88</v>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B628"/>
+  <dimension ref="A1:B629"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15045,6 +15066,16 @@
       </c>
       <c r="B628" t="n">
         <v>1.36</v>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B629" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -15207,28 +15238,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.413337848603623</v>
+        <v>1.419632258852086</v>
       </c>
       <c r="J2" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K2" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2235970692499609</v>
+        <v>0.2258631772922699</v>
       </c>
       <c r="M2" t="n">
-        <v>12.80482335774865</v>
+        <v>12.79091749278793</v>
       </c>
       <c r="N2" t="n">
-        <v>308.2734871363189</v>
+        <v>307.8325995558876</v>
       </c>
       <c r="O2" t="n">
-        <v>17.55771873383097</v>
+        <v>17.54515886379737</v>
       </c>
       <c r="P2" t="n">
-        <v>280.3371181530229</v>
+        <v>280.2583341525349</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15279,28 +15310,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5861111559299316</v>
+        <v>-0.5924377941336976</v>
       </c>
       <c r="J3" t="n">
+        <v>396</v>
+      </c>
+      <c r="K3" t="n">
         <v>395</v>
       </c>
-      <c r="K3" t="n">
-        <v>394</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01812643211654297</v>
+        <v>0.01860020886443059</v>
       </c>
       <c r="M3" t="n">
-        <v>19.33382838831832</v>
+        <v>19.30193483407107</v>
       </c>
       <c r="N3" t="n">
-        <v>828.9074208989597</v>
+        <v>827.1502457484833</v>
       </c>
       <c r="O3" t="n">
-        <v>28.7907523503461</v>
+        <v>28.76021984875086</v>
       </c>
       <c r="P3" t="n">
-        <v>240.8596079056245</v>
+        <v>240.9387107732413</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15351,28 +15382,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.501196137332423</v>
+        <v>-1.506342909693955</v>
       </c>
       <c r="J4" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="K4" t="n">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1650222552737496</v>
+        <v>0.1666289750438454</v>
       </c>
       <c r="M4" t="n">
-        <v>11.95113750873847</v>
+        <v>11.93821998919351</v>
       </c>
       <c r="N4" t="n">
-        <v>506.7927526989143</v>
+        <v>505.7386761572928</v>
       </c>
       <c r="O4" t="n">
-        <v>22.51205794011099</v>
+        <v>22.48863437733143</v>
       </c>
       <c r="P4" t="n">
-        <v>252.5126776786404</v>
+        <v>252.5770972668523</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15410,7 +15441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E396"/>
+  <dimension ref="A1:E397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26101,6 +26132,33 @@
         </is>
       </c>
     </row>
+    <row r="397">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>-36.89174472422115,174.98709446183662</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>-36.89223144066407,174.988556804702</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>-36.892917973489716,174.98872519467974</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8769,6 +8769,27 @@
       <c r="E397" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="n">
+        <v>329.74</v>
+      </c>
+      <c r="C398" t="n">
+        <v>214.73</v>
+      </c>
+      <c r="D398" t="n">
+        <v>202.54</v>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -8783,7 +8804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B629"/>
+  <dimension ref="A1:B633"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15076,6 +15097,46 @@
       </c>
       <c r="B629" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B630" t="n">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B631" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B632" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B633" t="n">
+        <v>0.43</v>
       </c>
     </row>
   </sheetData>
@@ -15238,28 +15299,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.419632258852086</v>
+        <v>1.42582510156851</v>
       </c>
       <c r="J2" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K2" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2258631772922699</v>
+        <v>0.2281170265212468</v>
       </c>
       <c r="M2" t="n">
-        <v>12.79091749278793</v>
+        <v>12.77670124854178</v>
       </c>
       <c r="N2" t="n">
-        <v>307.8325995558876</v>
+        <v>307.3854140926982</v>
       </c>
       <c r="O2" t="n">
-        <v>17.54515886379737</v>
+        <v>17.53241039026574</v>
       </c>
       <c r="P2" t="n">
-        <v>280.2583341525349</v>
+        <v>280.1806982035014</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15310,28 +15371,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5924377941336976</v>
+        <v>-0.5980288079530193</v>
       </c>
       <c r="J3" t="n">
+        <v>397</v>
+      </c>
+      <c r="K3" t="n">
         <v>396</v>
       </c>
-      <c r="K3" t="n">
-        <v>395</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.01860020886443059</v>
+        <v>0.01903737268184769</v>
       </c>
       <c r="M3" t="n">
-        <v>19.30193483407107</v>
+        <v>19.26816493974526</v>
       </c>
       <c r="N3" t="n">
-        <v>827.1502457484833</v>
+        <v>825.3292267856187</v>
       </c>
       <c r="O3" t="n">
-        <v>28.76021984875086</v>
+        <v>28.7285437637486</v>
       </c>
       <c r="P3" t="n">
-        <v>240.9387107732413</v>
+        <v>241.0087273903492</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15382,28 +15443,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.506342909693955</v>
+        <v>-1.511580779879383</v>
       </c>
       <c r="J4" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K4" t="n">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1666289750438454</v>
+        <v>0.1682578982128805</v>
       </c>
       <c r="M4" t="n">
-        <v>11.93821998919351</v>
+        <v>11.92581230155834</v>
       </c>
       <c r="N4" t="n">
-        <v>505.7386761572928</v>
+        <v>504.6995671434212</v>
       </c>
       <c r="O4" t="n">
-        <v>22.48863437733143</v>
+        <v>22.46551951643721</v>
       </c>
       <c r="P4" t="n">
-        <v>252.5770972668523</v>
+        <v>252.6427612989261</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15441,7 +15502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E397"/>
+  <dimension ref="A1:E398"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26159,6 +26220,33 @@
         </is>
       </c>
     </row>
+    <row r="398">
+      <c r="A398" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:54+00:00</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>-36.89174472422115,174.98709446183662</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>-36.89223369501941,174.9885436379381</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>-36.89291814530211,174.9887290031088</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0601/nzd0601.xlsx
+++ b/data/nzd0601/nzd0601.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="B398" t="n">
-        <v>329.74</v>
+        <v>318.4</v>
       </c>
       <c r="C398" t="n">
         <v>214.73</v>
@@ -8790,6 +8790,48 @@
       <c r="E398" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="n">
+        <v>308.47</v>
+      </c>
+      <c r="C399" t="n">
+        <v>211.44</v>
+      </c>
+      <c r="D399" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="n">
+        <v>300.84</v>
+      </c>
+      <c r="C400" t="n">
+        <v>211.13</v>
+      </c>
+      <c r="D400" t="n">
+        <v>199.82</v>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B633"/>
+  <dimension ref="A1:B636"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15137,6 +15179,36 @@
       </c>
       <c r="B633" t="n">
         <v>0.43</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B634" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B635" t="n">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B636" t="n">
+        <v>-0.9399999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -15299,28 +15371,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>1.42582510156851</v>
+        <v>1.404915237207437</v>
       </c>
       <c r="J2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K2" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2281170265212468</v>
+        <v>0.2243834604941952</v>
       </c>
       <c r="M2" t="n">
-        <v>12.77670124854178</v>
+        <v>12.78839775889906</v>
       </c>
       <c r="N2" t="n">
-        <v>307.3854140926982</v>
+        <v>306.52595702019</v>
       </c>
       <c r="O2" t="n">
-        <v>17.53241039026574</v>
+        <v>17.50788271094452</v>
       </c>
       <c r="P2" t="n">
-        <v>280.1806982035014</v>
+        <v>280.4435003641328</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15371,28 +15443,28 @@
         <v>0.0858</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5980288079530193</v>
+        <v>-0.612701683584034</v>
       </c>
       <c r="J3" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K3" t="n">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01903737268184769</v>
+        <v>0.02014763936589159</v>
       </c>
       <c r="M3" t="n">
-        <v>19.26816493974526</v>
+        <v>19.21010441612573</v>
       </c>
       <c r="N3" t="n">
-        <v>825.3292267856187</v>
+        <v>822.1039364329781</v>
       </c>
       <c r="O3" t="n">
-        <v>28.7285437637486</v>
+        <v>28.67235491606816</v>
       </c>
       <c r="P3" t="n">
-        <v>241.0087273903492</v>
+        <v>241.1930983505746</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15443,28 +15515,28 @@
         <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.511580779879383</v>
+        <v>-1.52485677165041</v>
       </c>
       <c r="J4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="K4" t="n">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1682578982128805</v>
+        <v>0.171989604094916</v>
       </c>
       <c r="M4" t="n">
-        <v>11.92581230155834</v>
+        <v>11.91083312861827</v>
       </c>
       <c r="N4" t="n">
-        <v>504.6995671434212</v>
+        <v>502.9241490290441</v>
       </c>
       <c r="O4" t="n">
-        <v>22.46551951643721</v>
+        <v>22.42597041443344</v>
       </c>
       <c r="P4" t="n">
-        <v>252.6427612989261</v>
+        <v>252.8097526134511</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15502,7 +15574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E398"/>
+  <dimension ref="A1:E400"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26228,7 +26300,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>-36.89174472422115,174.98709446183662</t>
+          <t>-36.89172342203444,174.9872188874073</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -26244,6 +26316,60 @@
       <c r="E398" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-24 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>-36.891704768426884,174.9873278420121</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>-36.89222751432509,174.98857973681382</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>-36.892919681501574,174.98876305494542</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:11:18+00:00</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>-36.89169043532618,174.98741156036527</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>-36.892226931949075,174.9885831382273</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>-36.89291951979683,174.9887594705415</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
